--- a/output/2016-2020/round2_check_20261002/round2_check_value_diffs_20261002_check.xlsx
+++ b/output/2016-2020/round2_check_20261002/round2_check_value_diffs_20261002_check.xlsx
@@ -1,20 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://intlmonetaryfund-my.sharepoint.com/personal/xli7_imf_org/Documents/Shelley_My Projects/SFA/output/2016-2020/round2_check_20261002/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="637" documentId="8_{0D36A3F1-0F2E-4329-AD07-5EB667F35DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32743550-25D6-4768-B0F2-18F1D4ED95FE}"/>
+  <xr:revisionPtr revIDLastSave="684" documentId="8_{0D36A3F1-0F2E-4329-AD07-5EB667F35DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6D8CD81-FD5A-4DF0-9DD6-DA6F1DD87D42}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{CBE37347-7A94-4860-8077-65AAB5D354B3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{CBE37347-7A94-4860-8077-65AAB5D354B3}"/>
   </bookViews>
   <sheets>
     <sheet name="round2_check_value_diffs_202610" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="BoxPlot">"BoxPlot"</definedName>
+    <definedName name="Bubble">"Bubble"</definedName>
+    <definedName name="Candlestick">"Candlestick"</definedName>
+    <definedName name="Chart">"Chart"</definedName>
+    <definedName name="ChartImage">"ChartImage"</definedName>
+    <definedName name="ColumnRange">"ColumnRange"</definedName>
+    <definedName name="Dumbbell">"Dumbbell"</definedName>
+    <definedName name="Heatmap">"Heatmap"</definedName>
+    <definedName name="Histogram">"Histogram"</definedName>
+    <definedName name="IQ_CH">110000</definedName>
+    <definedName name="IQ_CQ">5000</definedName>
+    <definedName name="IQ_CY">10000</definedName>
+    <definedName name="IQ_DAILY">500000</definedName>
+    <definedName name="IQ_FH">100000</definedName>
+    <definedName name="IQ_FQ">500</definedName>
+    <definedName name="IQ_FWD_CY" hidden="1">10001</definedName>
+    <definedName name="IQ_FWD_CY1" hidden="1">10002</definedName>
+    <definedName name="IQ_FWD_CY2" hidden="1">10003</definedName>
+    <definedName name="IQ_FWD_FY" hidden="1">1001</definedName>
+    <definedName name="IQ_FWD_FY1" hidden="1">1002</definedName>
+    <definedName name="IQ_FWD_FY2" hidden="1">1003</definedName>
+    <definedName name="IQ_FWD_Q" hidden="1">501</definedName>
+    <definedName name="IQ_FWD_Q1" hidden="1">502</definedName>
+    <definedName name="IQ_FWD_Q2" hidden="1">503</definedName>
+    <definedName name="IQ_FY">1000</definedName>
+    <definedName name="IQ_LATESTK" hidden="1">1000</definedName>
+    <definedName name="IQ_LATESTQ" hidden="1">500</definedName>
+    <definedName name="IQ_LTM">2000</definedName>
+    <definedName name="IQ_LTMMONTH" hidden="1">120000</definedName>
+    <definedName name="IQ_MONTH">15000</definedName>
+    <definedName name="IQ_NTM">6000</definedName>
+    <definedName name="IQ_TODAY" hidden="1">0</definedName>
+    <definedName name="IQ_WEEK">50000</definedName>
+    <definedName name="IQ_YTD">3000</definedName>
+    <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
+    <definedName name="Map">"Map"</definedName>
+    <definedName name="OHLC">"OHLC"</definedName>
+    <definedName name="PieChart">"PieChart"</definedName>
+    <definedName name="Scatter">"Scatter"</definedName>
+    <definedName name="Series">"Series"</definedName>
+    <definedName name="Stripe">"Stripe"</definedName>
+    <definedName name="Table">"Table"</definedName>
+    <definedName name="TreeMap">"TreeMap"</definedName>
+    <definedName name="Waterfall">"Waterfall"</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -3592,7 +3638,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -4101,7 +4147,9 @@
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{3684C28E-DC09-426D-803A-2E5603E4D6E3}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -4431,16 +4479,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB24D95-2BC8-4DA5-B99B-D2D7C02B9712}">
   <dimension ref="A1:S957"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="0" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="31.77734375" customWidth="1"/>
-    <col min="6" max="6" width="39.5546875" customWidth="1"/>
-    <col min="7" max="8" width="8.88671875" hidden="1" customWidth="1"/>
-    <col min="12" max="17" width="8.88671875" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" customWidth="1"/>
+    <col min="6" max="6" width="39.5703125" customWidth="1"/>
+    <col min="7" max="8" width="8.85546875" hidden="1" customWidth="1"/>
+    <col min="12" max="17" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4499,7 +4547,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -4552,7 +4600,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -4605,7 +4653,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -4658,7 +4706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -4711,7 +4759,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -4764,7 +4812,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -4817,7 +4865,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -4870,7 +4918,7 @@
         <v>-1.8</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -4923,7 +4971,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -4976,7 +5024,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -5029,7 +5077,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -5082,7 +5130,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -5135,7 +5183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -5188,7 +5236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -5241,7 +5289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -5294,7 +5342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>56</v>
       </c>
@@ -5347,7 +5395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -5400,7 +5448,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -5453,7 +5501,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -5506,7 +5554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -5559,7 +5607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>69</v>
       </c>
@@ -5612,7 +5660,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>71</v>
       </c>
@@ -5665,7 +5713,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>72</v>
       </c>
@@ -5718,7 +5766,7 @@
         <v>-0.9</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>74</v>
       </c>
@@ -5771,7 +5819,7 @@
         <v>-0.9</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>76</v>
       </c>
@@ -5824,7 +5872,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -5877,7 +5925,7 @@
         <v>-2.6</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -5930,7 +5978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -5983,7 +6031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>84</v>
       </c>
@@ -6036,7 +6084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>86</v>
       </c>
@@ -6089,7 +6137,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -6148,7 +6196,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>93</v>
       </c>
@@ -6207,7 +6255,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>94</v>
       </c>
@@ -6266,7 +6314,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>95</v>
       </c>
@@ -6325,7 +6373,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>96</v>
       </c>
@@ -6384,7 +6432,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>97</v>
       </c>
@@ -6443,7 +6491,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>98</v>
       </c>
@@ -6502,7 +6550,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>99</v>
       </c>
@@ -6561,7 +6609,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>100</v>
       </c>
@@ -6620,7 +6668,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>101</v>
       </c>
@@ -6679,7 +6727,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>102</v>
       </c>
@@ -6738,7 +6786,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>103</v>
       </c>
@@ -6797,7 +6845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>104</v>
       </c>
@@ -6856,7 +6904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>105</v>
       </c>
@@ -6915,7 +6963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>106</v>
       </c>
@@ -6974,7 +7022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>107</v>
       </c>
@@ -7033,7 +7081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>108</v>
       </c>
@@ -7092,7 +7140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -7145,7 +7193,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>113</v>
       </c>
@@ -7198,7 +7246,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>114</v>
       </c>
@@ -7251,7 +7299,7 @@
         <v>-1.9</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -7304,7 +7352,7 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>116</v>
       </c>
@@ -7357,7 +7405,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>117</v>
       </c>
@@ -7410,7 +7458,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>118</v>
       </c>
@@ -7463,7 +7511,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>119</v>
       </c>
@@ -7516,7 +7564,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>120</v>
       </c>
@@ -7569,7 +7617,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>121</v>
       </c>
@@ -7622,7 +7670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>122</v>
       </c>
@@ -7675,7 +7723,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>123</v>
       </c>
@@ -7728,7 +7776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>126</v>
       </c>
@@ -7781,7 +7829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>127</v>
       </c>
@@ -7834,7 +7882,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>130</v>
       </c>
@@ -7887,7 +7935,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>132</v>
       </c>
@@ -7946,7 +7994,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>136</v>
       </c>
@@ -8005,7 +8053,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>137</v>
       </c>
@@ -8064,7 +8112,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>138</v>
       </c>
@@ -8123,7 +8171,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>139</v>
       </c>
@@ -8182,7 +8230,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>140</v>
       </c>
@@ -8241,7 +8289,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>141</v>
       </c>
@@ -8300,7 +8348,7 @@
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>142</v>
       </c>
@@ -8359,7 +8407,7 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>143</v>
       </c>
@@ -8418,7 +8466,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>144</v>
       </c>
@@ -8477,7 +8525,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>145</v>
       </c>
@@ -8536,7 +8584,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>146</v>
       </c>
@@ -8595,7 +8643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>147</v>
       </c>
@@ -8654,7 +8702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>148</v>
       </c>
@@ -8713,7 +8761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>149</v>
       </c>
@@ -8772,7 +8820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>150</v>
       </c>
@@ -8831,7 +8879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>151</v>
       </c>
@@ -8890,7 +8938,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>152</v>
       </c>
@@ -8949,7 +8997,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>156</v>
       </c>
@@ -9008,7 +9056,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>157</v>
       </c>
@@ -9067,7 +9115,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C84" t="s">
         <v>154</v>
       </c>
@@ -9087,7 +9135,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C85" t="s">
         <v>154</v>
       </c>
@@ -9107,7 +9155,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C86" t="s">
         <v>154</v>
       </c>
@@ -9127,7 +9175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C87" t="s">
         <v>154</v>
       </c>
@@ -9147,7 +9195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C88" t="s">
         <v>154</v>
       </c>
@@ -9167,7 +9215,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>159</v>
       </c>
@@ -9226,7 +9274,7 @@
         <v>-3.7</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>163</v>
       </c>
@@ -9285,7 +9333,7 @@
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>164</v>
       </c>
@@ -9344,7 +9392,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>165</v>
       </c>
@@ -9403,7 +9451,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>166</v>
       </c>
@@ -9462,7 +9510,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>167</v>
       </c>
@@ -9521,7 +9569,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>169</v>
       </c>
@@ -9580,7 +9628,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>173</v>
       </c>
@@ -9639,7 +9687,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>174</v>
       </c>
@@ -9698,7 +9746,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>176</v>
       </c>
@@ -9757,7 +9805,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>177</v>
       </c>
@@ -9816,7 +9864,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>178</v>
       </c>
@@ -9875,7 +9923,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>179</v>
       </c>
@@ -9934,7 +9982,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>180</v>
       </c>
@@ -9993,7 +10041,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>181</v>
       </c>
@@ -10052,7 +10100,7 @@
         <v>-1.9</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>182</v>
       </c>
@@ -10111,7 +10159,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>183</v>
       </c>
@@ -10170,7 +10218,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>184</v>
       </c>
@@ -10229,7 +10277,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>185</v>
       </c>
@@ -10288,7 +10336,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>186</v>
       </c>
@@ -10347,7 +10395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>187</v>
       </c>
@@ -10406,7 +10454,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>188</v>
       </c>
@@ -10465,7 +10513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>189</v>
       </c>
@@ -10524,7 +10572,7 @@
         <v>-1.9</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>190</v>
       </c>
@@ -10583,7 +10631,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>193</v>
       </c>
@@ -10642,7 +10690,7 @@
         <v>-3.8</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>194</v>
       </c>
@@ -10701,7 +10749,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>195</v>
       </c>
@@ -10760,7 +10808,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>196</v>
       </c>
@@ -10819,7 +10867,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>197</v>
       </c>
@@ -10878,7 +10926,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>198</v>
       </c>
@@ -10937,7 +10985,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>199</v>
       </c>
@@ -10996,7 +11044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>200</v>
       </c>
@@ -11055,7 +11103,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>201</v>
       </c>
@@ -11114,7 +11162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>202</v>
       </c>
@@ -11173,7 +11221,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>203</v>
       </c>
@@ -11232,7 +11280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>204</v>
       </c>
@@ -11291,7 +11339,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>205</v>
       </c>
@@ -11350,7 +11398,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>209</v>
       </c>
@@ -11409,7 +11457,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>210</v>
       </c>
@@ -11468,7 +11516,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>211</v>
       </c>
@@ -11527,7 +11575,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>212</v>
       </c>
@@ -11586,7 +11634,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>213</v>
       </c>
@@ -11645,7 +11693,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>214</v>
       </c>
@@ -11704,7 +11752,7 @@
         <v>-1.3</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>215</v>
       </c>
@@ -11763,7 +11811,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>216</v>
       </c>
@@ -11822,7 +11870,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>217</v>
       </c>
@@ -11881,7 +11929,7 @@
         <v>-3.1</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>218</v>
       </c>
@@ -11940,7 +11988,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>219</v>
       </c>
@@ -11999,7 +12047,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>220</v>
       </c>
@@ -12058,7 +12106,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>221</v>
       </c>
@@ -12117,7 +12165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>222</v>
       </c>
@@ -12176,7 +12224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>223</v>
       </c>
@@ -12235,7 +12283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>224</v>
       </c>
@@ -12294,7 +12342,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>225</v>
       </c>
@@ -12353,7 +12401,7 @@
         <v>-1.3</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>228</v>
       </c>
@@ -12412,7 +12460,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>229</v>
       </c>
@@ -12471,7 +12519,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>230</v>
       </c>
@@ -12530,7 +12578,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>231</v>
       </c>
@@ -12589,7 +12637,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>232</v>
       </c>
@@ -12648,7 +12696,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>233</v>
       </c>
@@ -12707,7 +12755,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>234</v>
       </c>
@@ -12766,7 +12814,7 @@
         <v>-1.3</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>235</v>
       </c>
@@ -12825,7 +12873,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>236</v>
       </c>
@@ -12884,7 +12932,7 @@
         <v>-2.4</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>237</v>
       </c>
@@ -12943,7 +12991,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>238</v>
       </c>
@@ -13002,7 +13050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>239</v>
       </c>
@@ -13061,7 +13109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>240</v>
       </c>
@@ -13120,7 +13168,7 @@
         <v>-1.9</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>241</v>
       </c>
@@ -13179,7 +13227,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>245</v>
       </c>
@@ -13238,7 +13286,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>246</v>
       </c>
@@ -13297,7 +13345,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>247</v>
       </c>
@@ -13356,7 +13404,7 @@
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>248</v>
       </c>
@@ -13415,7 +13463,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>249</v>
       </c>
@@ -13474,7 +13522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>250</v>
       </c>
@@ -13533,7 +13581,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>251</v>
       </c>
@@ -13592,7 +13640,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>252</v>
       </c>
@@ -13651,7 +13699,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>253</v>
       </c>
@@ -13701,7 +13749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>254</v>
       </c>
@@ -13760,7 +13808,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>255</v>
       </c>
@@ -13819,7 +13867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>258</v>
       </c>
@@ -13878,7 +13926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>259</v>
       </c>
@@ -13937,7 +13985,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>261</v>
       </c>
@@ -13996,7 +14044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>262</v>
       </c>
@@ -14055,7 +14103,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>266</v>
       </c>
@@ -14114,7 +14162,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>267</v>
       </c>
@@ -14173,7 +14221,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>268</v>
       </c>
@@ -14232,7 +14280,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>269</v>
       </c>
@@ -14291,7 +14339,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>270</v>
       </c>
@@ -14350,7 +14398,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>271</v>
       </c>
@@ -14409,7 +14457,7 @@
         <v>-3.2</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>272</v>
       </c>
@@ -14468,7 +14516,7 @@
         <v>-2.7</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>273</v>
       </c>
@@ -14527,7 +14575,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>274</v>
       </c>
@@ -14586,7 +14634,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>275</v>
       </c>
@@ -14645,7 +14693,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>276</v>
       </c>
@@ -14704,7 +14752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>277</v>
       </c>
@@ -14763,7 +14811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>278</v>
       </c>
@@ -14822,7 +14870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>279</v>
       </c>
@@ -14881,7 +14929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>280</v>
       </c>
@@ -14940,7 +14988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>281</v>
       </c>
@@ -14999,7 +15047,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>282</v>
       </c>
@@ -15058,7 +15106,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>285</v>
       </c>
@@ -15117,7 +15165,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>286</v>
       </c>
@@ -15176,7 +15224,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>287</v>
       </c>
@@ -15235,7 +15283,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>288</v>
       </c>
@@ -15294,7 +15342,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>289</v>
       </c>
@@ -15353,7 +15401,7 @@
         <v>-3.9</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>290</v>
       </c>
@@ -15412,7 +15460,7 @@
         <v>-2.9</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>291</v>
       </c>
@@ -15471,7 +15519,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>292</v>
       </c>
@@ -15530,7 +15578,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C197" t="s">
         <v>284</v>
       </c>
@@ -15550,7 +15598,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C198" t="s">
         <v>284</v>
       </c>
@@ -15570,7 +15618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C199" t="s">
         <v>284</v>
       </c>
@@ -15590,7 +15638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C200" t="s">
         <v>284</v>
       </c>
@@ -15610,7 +15658,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C201" t="s">
         <v>284</v>
       </c>
@@ -15630,7 +15678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>293</v>
       </c>
@@ -15689,7 +15737,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>294</v>
       </c>
@@ -15748,7 +15796,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>298</v>
       </c>
@@ -15807,7 +15855,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>299</v>
       </c>
@@ -15866,7 +15914,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>300</v>
       </c>
@@ -15925,7 +15973,7 @@
         <v>37.200000000000003</v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>301</v>
       </c>
@@ -15984,7 +16032,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>302</v>
       </c>
@@ -16043,7 +16091,7 @@
         <v>58.1</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>303</v>
       </c>
@@ -16102,7 +16150,7 @@
         <v>-3.5</v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>304</v>
       </c>
@@ -16161,7 +16209,7 @@
         <v>-3.3</v>
       </c>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>305</v>
       </c>
@@ -16220,7 +16268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>306</v>
       </c>
@@ -16279,7 +16327,7 @@
         <v>-3.3</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>307</v>
       </c>
@@ -16338,7 +16386,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>308</v>
       </c>
@@ -16397,7 +16445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>309</v>
       </c>
@@ -16456,7 +16504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>310</v>
       </c>
@@ -16515,7 +16563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>311</v>
       </c>
@@ -16574,7 +16622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>312</v>
       </c>
@@ -16633,7 +16681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>313</v>
       </c>
@@ -16692,7 +16740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C220" t="s">
         <v>316</v>
       </c>
@@ -16712,7 +16760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C221" t="s">
         <v>316</v>
       </c>
@@ -16732,7 +16780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C222" t="s">
         <v>316</v>
       </c>
@@ -16752,7 +16800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C223" t="s">
         <v>316</v>
       </c>
@@ -16772,7 +16820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C224" t="s">
         <v>316</v>
       </c>
@@ -16792,7 +16840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>314</v>
       </c>
@@ -16842,7 +16890,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>319</v>
       </c>
@@ -16901,7 +16949,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>323</v>
       </c>
@@ -16960,7 +17008,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>324</v>
       </c>
@@ -17019,7 +17067,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>325</v>
       </c>
@@ -17078,7 +17126,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>326</v>
       </c>
@@ -17137,7 +17185,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>327</v>
       </c>
@@ -17196,7 +17244,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>328</v>
       </c>
@@ -17255,7 +17303,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>329</v>
       </c>
@@ -17314,7 +17362,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>330</v>
       </c>
@@ -17373,7 +17421,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>331</v>
       </c>
@@ -17423,7 +17471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>332</v>
       </c>
@@ -17482,7 +17530,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>333</v>
       </c>
@@ -17541,7 +17589,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>335</v>
       </c>
@@ -17600,7 +17648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>336</v>
       </c>
@@ -17659,7 +17707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>338</v>
       </c>
@@ -17718,7 +17766,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>339</v>
       </c>
@@ -17777,7 +17825,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>343</v>
       </c>
@@ -17836,7 +17884,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>344</v>
       </c>
@@ -17895,7 +17943,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>345</v>
       </c>
@@ -17954,7 +18002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>346</v>
       </c>
@@ -18013,7 +18061,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>347</v>
       </c>
@@ -18072,7 +18120,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>348</v>
       </c>
@@ -18131,7 +18179,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>349</v>
       </c>
@@ -18190,7 +18238,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>350</v>
       </c>
@@ -18249,7 +18297,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>351</v>
       </c>
@@ -18308,7 +18356,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>352</v>
       </c>
@@ -18367,7 +18415,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>353</v>
       </c>
@@ -18426,7 +18474,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>355</v>
       </c>
@@ -18485,7 +18533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>356</v>
       </c>
@@ -18544,7 +18592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>360</v>
       </c>
@@ -18603,7 +18651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>361</v>
       </c>
@@ -18662,7 +18710,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>365</v>
       </c>
@@ -18721,7 +18769,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>366</v>
       </c>
@@ -18780,7 +18828,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>367</v>
       </c>
@@ -18839,7 +18887,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>368</v>
       </c>
@@ -18898,7 +18946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>369</v>
       </c>
@@ -18957,7 +19005,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>370</v>
       </c>
@@ -19016,7 +19064,7 @@
         <v>-4.8</v>
       </c>
     </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>371</v>
       </c>
@@ -19075,7 +19123,7 @@
         <v>-4.5999999999999996</v>
       </c>
     </row>
-    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>372</v>
       </c>
@@ -19134,7 +19182,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>373</v>
       </c>
@@ -19193,7 +19241,7 @@
         <v>-2.9</v>
       </c>
     </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>374</v>
       </c>
@@ -19252,7 +19300,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>375</v>
       </c>
@@ -19311,7 +19359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>376</v>
       </c>
@@ -19370,7 +19418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>377</v>
       </c>
@@ -19429,7 +19477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>378</v>
       </c>
@@ -19488,7 +19536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>379</v>
       </c>
@@ -19547,7 +19595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>380</v>
       </c>
@@ -19606,7 +19654,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>381</v>
       </c>
@@ -19665,7 +19713,7 @@
         <v>-3.3</v>
       </c>
     </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>385</v>
       </c>
@@ -19724,7 +19772,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="275" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>386</v>
       </c>
@@ -19783,7 +19831,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>387</v>
       </c>
@@ -19842,7 +19890,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>388</v>
       </c>
@@ -19901,7 +19949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>389</v>
       </c>
@@ -19960,7 +20008,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>390</v>
       </c>
@@ -20019,7 +20067,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="280" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>391</v>
       </c>
@@ -20078,7 +20126,7 @@
         <v>-0.9</v>
       </c>
     </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>392</v>
       </c>
@@ -20137,7 +20185,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>393</v>
       </c>
@@ -20196,7 +20244,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>394</v>
       </c>
@@ -20255,7 +20303,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>395</v>
       </c>
@@ -20314,7 +20362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>396</v>
       </c>
@@ -20373,7 +20421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>397</v>
       </c>
@@ -20432,7 +20480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>398</v>
       </c>
@@ -20491,7 +20539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>399</v>
       </c>
@@ -20550,7 +20598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>400</v>
       </c>
@@ -20609,7 +20657,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>401</v>
       </c>
@@ -20668,7 +20716,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>404</v>
       </c>
@@ -20727,7 +20775,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>405</v>
       </c>
@@ -20786,7 +20834,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="293" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>406</v>
       </c>
@@ -20845,7 +20893,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="294" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>407</v>
       </c>
@@ -20904,7 +20952,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="295" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>408</v>
       </c>
@@ -20963,7 +21011,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="296" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>409</v>
       </c>
@@ -21022,7 +21070,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="297" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>410</v>
       </c>
@@ -21081,7 +21129,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="298" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>411</v>
       </c>
@@ -21140,7 +21188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>412</v>
       </c>
@@ -21199,7 +21247,7 @@
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="300" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>413</v>
       </c>
@@ -21258,7 +21306,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="301" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>414</v>
       </c>
@@ -21317,7 +21365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>415</v>
       </c>
@@ -21376,7 +21424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>416</v>
       </c>
@@ -21435,7 +21483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>417</v>
       </c>
@@ -21494,7 +21542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>418</v>
       </c>
@@ -21553,7 +21601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>419</v>
       </c>
@@ -21612,7 +21660,7 @@
         <v>-3.2</v>
       </c>
     </row>
-    <row r="307" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>420</v>
       </c>
@@ -21671,7 +21719,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="308" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>424</v>
       </c>
@@ -21730,7 +21778,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="309" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>425</v>
       </c>
@@ -21789,7 +21837,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="310" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>426</v>
       </c>
@@ -21848,7 +21896,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="311" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>427</v>
       </c>
@@ -21907,7 +21955,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="312" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C312" t="s">
         <v>422</v>
       </c>
@@ -21927,7 +21975,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="313" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C313" t="s">
         <v>422</v>
       </c>
@@ -21947,7 +21995,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="314" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C314" t="s">
         <v>422</v>
       </c>
@@ -21967,7 +22015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C315" t="s">
         <v>422</v>
       </c>
@@ -21987,7 +22035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C316" t="s">
         <v>422</v>
       </c>
@@ -22007,7 +22055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C317" t="s">
         <v>422</v>
       </c>
@@ -22027,7 +22075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C318" t="s">
         <v>422</v>
       </c>
@@ -22047,7 +22095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C319" t="s">
         <v>422</v>
       </c>
@@ -22067,7 +22115,7 @@
         <v>-2.2000000000000002</v>
       </c>
     </row>
-    <row r="320" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>428</v>
       </c>
@@ -22126,7 +22174,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="321" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>432</v>
       </c>
@@ -22185,7 +22233,7 @@
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>433</v>
       </c>
@@ -22244,7 +22292,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="323" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>434</v>
       </c>
@@ -22303,7 +22351,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="324" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>435</v>
       </c>
@@ -22362,7 +22410,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="325" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>436</v>
       </c>
@@ -22421,7 +22469,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="326" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>437</v>
       </c>
@@ -22480,7 +22528,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="327" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>438</v>
       </c>
@@ -22539,7 +22587,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="328" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>439</v>
       </c>
@@ -22598,7 +22646,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="329" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>440</v>
       </c>
@@ -22657,7 +22705,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="330" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>441</v>
       </c>
@@ -22716,7 +22764,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="331" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>442</v>
       </c>
@@ -22775,7 +22823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>443</v>
       </c>
@@ -22834,7 +22882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>444</v>
       </c>
@@ -22893,7 +22941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>445</v>
       </c>
@@ -22952,7 +23000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>446</v>
       </c>
@@ -23011,7 +23059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>447</v>
       </c>
@@ -23070,7 +23118,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="337" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>448</v>
       </c>
@@ -23123,7 +23171,7 @@
         <v>-5.8</v>
       </c>
     </row>
-    <row r="338" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>452</v>
       </c>
@@ -23176,7 +23224,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="339" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>453</v>
       </c>
@@ -23229,7 +23277,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="340" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>454</v>
       </c>
@@ -23282,7 +23330,7 @@
         <v>40.9</v>
       </c>
     </row>
-    <row r="341" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>455</v>
       </c>
@@ -23335,7 +23383,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="342" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>456</v>
       </c>
@@ -23388,7 +23436,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="343" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>457</v>
       </c>
@@ -23441,7 +23489,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="344" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>458</v>
       </c>
@@ -23494,7 +23542,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="345" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>459</v>
       </c>
@@ -23547,7 +23595,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="346" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>460</v>
       </c>
@@ -23600,7 +23648,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="347" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>461</v>
       </c>
@@ -23653,7 +23701,7 @@
         <v>-4.2</v>
       </c>
     </row>
-    <row r="348" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>462</v>
       </c>
@@ -23706,7 +23754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>463</v>
       </c>
@@ -23759,7 +23807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>464</v>
       </c>
@@ -23812,7 +23860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>465</v>
       </c>
@@ -23865,7 +23913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>466</v>
       </c>
@@ -23918,7 +23966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>467</v>
       </c>
@@ -23971,7 +24019,7 @@
         <v>-6.3</v>
       </c>
     </row>
-    <row r="354" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>468</v>
       </c>
@@ -24024,7 +24072,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="355" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>472</v>
       </c>
@@ -24077,7 +24125,7 @@
         <v>-12.2</v>
       </c>
     </row>
-    <row r="356" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>473</v>
       </c>
@@ -24130,7 +24178,7 @@
         <v>-11.3</v>
       </c>
     </row>
-    <row r="357" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>474</v>
       </c>
@@ -24183,7 +24231,7 @@
         <v>125.8</v>
       </c>
     </row>
-    <row r="358" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>475</v>
       </c>
@@ -24236,7 +24284,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="359" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>476</v>
       </c>
@@ -24289,7 +24337,7 @@
         <v>114.5</v>
       </c>
     </row>
-    <row r="360" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>477</v>
       </c>
@@ -24342,7 +24390,7 @@
         <v>-0.9</v>
       </c>
     </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>478</v>
       </c>
@@ -24395,7 +24443,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>479</v>
       </c>
@@ -24448,7 +24496,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>480</v>
       </c>
@@ -24501,7 +24549,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>481</v>
       </c>
@@ -24554,7 +24602,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>482</v>
       </c>
@@ -24607,7 +24655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>483</v>
       </c>
@@ -24660,7 +24708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>484</v>
       </c>
@@ -24713,7 +24761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>487</v>
       </c>
@@ -24766,7 +24814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>488</v>
       </c>
@@ -24819,7 +24867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>490</v>
       </c>
@@ -24872,7 +24920,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>491</v>
       </c>
@@ -24925,7 +24973,7 @@
         <v>-6.8</v>
       </c>
     </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>495</v>
       </c>
@@ -24978,7 +25026,7 @@
         <v>-2.6</v>
       </c>
     </row>
-    <row r="373" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>496</v>
       </c>
@@ -25031,7 +25079,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>497</v>
       </c>
@@ -25084,7 +25132,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="375" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>498</v>
       </c>
@@ -25137,7 +25185,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>499</v>
       </c>
@@ -25190,7 +25238,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>500</v>
       </c>
@@ -25243,7 +25291,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="378" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>501</v>
       </c>
@@ -25296,7 +25344,7 @@
         <v>-2.4</v>
       </c>
     </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>502</v>
       </c>
@@ -25349,7 +25397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>503</v>
       </c>
@@ -25402,7 +25450,7 @@
         <v>-2.4</v>
       </c>
     </row>
-    <row r="381" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>504</v>
       </c>
@@ -25455,7 +25503,7 @@
         <v>-5.6</v>
       </c>
     </row>
-    <row r="382" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>505</v>
       </c>
@@ -25508,7 +25556,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="383" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>506</v>
       </c>
@@ -25561,7 +25609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>507</v>
       </c>
@@ -25614,7 +25662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>508</v>
       </c>
@@ -25667,7 +25715,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="386" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>509</v>
       </c>
@@ -25720,7 +25768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>510</v>
       </c>
@@ -25773,7 +25821,7 @@
         <v>-4.0999999999999996</v>
       </c>
     </row>
-    <row r="388" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>511</v>
       </c>
@@ -25826,7 +25874,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="389" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>515</v>
       </c>
@@ -25879,7 +25927,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="390" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>516</v>
       </c>
@@ -25932,7 +25980,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="391" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>517</v>
       </c>
@@ -25985,7 +26033,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>518</v>
       </c>
@@ -26038,7 +26086,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="393" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>519</v>
       </c>
@@ -26091,7 +26139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>520</v>
       </c>
@@ -26144,7 +26192,7 @@
         <v>-2.7</v>
       </c>
     </row>
-    <row r="395" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>521</v>
       </c>
@@ -26197,7 +26245,7 @@
         <v>-3.7</v>
       </c>
     </row>
-    <row r="396" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>522</v>
       </c>
@@ -26250,7 +26298,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="397" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>523</v>
       </c>
@@ -26303,7 +26351,7 @@
         <v>-4.5</v>
       </c>
     </row>
-    <row r="398" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>524</v>
       </c>
@@ -26356,7 +26404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>525</v>
       </c>
@@ -26409,7 +26457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>526</v>
       </c>
@@ -26462,7 +26510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>527</v>
       </c>
@@ -26515,7 +26563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>528</v>
       </c>
@@ -26568,7 +26616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>529</v>
       </c>
@@ -26621,7 +26669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>530</v>
       </c>
@@ -26674,7 +26722,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="405" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>531</v>
       </c>
@@ -26727,7 +26775,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="406" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>534</v>
       </c>
@@ -26780,7 +26828,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="407" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>535</v>
       </c>
@@ -26833,7 +26881,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="408" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>536</v>
       </c>
@@ -26886,7 +26934,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="409" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>537</v>
       </c>
@@ -26939,7 +26987,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="410" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>538</v>
       </c>
@@ -26992,7 +27040,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>539</v>
       </c>
@@ -27045,7 +27093,7 @@
         <v>-4.3</v>
       </c>
     </row>
-    <row r="412" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>540</v>
       </c>
@@ -27098,7 +27146,7 @@
         <v>-3.8</v>
       </c>
     </row>
-    <row r="413" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>541</v>
       </c>
@@ -27151,7 +27199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>542</v>
       </c>
@@ -27204,7 +27252,7 @@
         <v>-3.8</v>
       </c>
     </row>
-    <row r="415" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>543</v>
       </c>
@@ -27257,7 +27305,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="416" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>544</v>
       </c>
@@ -27310,7 +27358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>545</v>
       </c>
@@ -27363,7 +27411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>546</v>
       </c>
@@ -27416,7 +27464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>547</v>
       </c>
@@ -27469,7 +27517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>548</v>
       </c>
@@ -27522,7 +27570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>549</v>
       </c>
@@ -27575,7 +27623,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="422" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>550</v>
       </c>
@@ -27628,7 +27676,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="423" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>555</v>
       </c>
@@ -27681,7 +27729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>556</v>
       </c>
@@ -27734,7 +27782,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="425" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>557</v>
       </c>
@@ -27787,7 +27835,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="426" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>558</v>
       </c>
@@ -27840,7 +27888,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="427" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>559</v>
       </c>
@@ -27893,7 +27941,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="428" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>560</v>
       </c>
@@ -27946,7 +27994,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="429" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>561</v>
       </c>
@@ -27999,7 +28047,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="430" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>562</v>
       </c>
@@ -28052,7 +28100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>563</v>
       </c>
@@ -28105,7 +28153,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="432" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>564</v>
       </c>
@@ -28158,7 +28206,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="433" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>565</v>
       </c>
@@ -28211,7 +28259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>566</v>
       </c>
@@ -28264,7 +28312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>567</v>
       </c>
@@ -28317,7 +28365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>568</v>
       </c>
@@ -28370,7 +28418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>569</v>
       </c>
@@ -28423,7 +28471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>570</v>
       </c>
@@ -28476,7 +28524,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="439" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>571</v>
       </c>
@@ -28529,7 +28577,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="440" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>574</v>
       </c>
@@ -28582,7 +28630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="441" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>575</v>
       </c>
@@ -28635,7 +28683,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="442" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>576</v>
       </c>
@@ -28688,7 +28736,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="443" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>577</v>
       </c>
@@ -28741,7 +28789,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="444" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>578</v>
       </c>
@@ -28794,7 +28842,7 @@
         <v>35.299999999999997</v>
       </c>
     </row>
-    <row r="445" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>579</v>
       </c>
@@ -28847,7 +28895,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="446" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>580</v>
       </c>
@@ -28900,7 +28948,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="447" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>581</v>
       </c>
@@ -28953,7 +29001,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="448" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>582</v>
       </c>
@@ -29006,7 +29054,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="449" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>583</v>
       </c>
@@ -29059,7 +29107,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="450" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>584</v>
       </c>
@@ -29112,7 +29160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>585</v>
       </c>
@@ -29165,7 +29213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>586</v>
       </c>
@@ -29218,7 +29266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>587</v>
       </c>
@@ -29271,7 +29319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>588</v>
       </c>
@@ -29324,7 +29372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>589</v>
       </c>
@@ -29377,7 +29425,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="456" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>590</v>
       </c>
@@ -29430,7 +29478,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="457" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>593</v>
       </c>
@@ -29483,7 +29531,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="458" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>594</v>
       </c>
@@ -29536,7 +29584,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="459" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>595</v>
       </c>
@@ -29589,7 +29637,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="460" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>596</v>
       </c>
@@ -29642,7 +29690,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="461" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>597</v>
       </c>
@@ -29695,7 +29743,7 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="462" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>598</v>
       </c>
@@ -29748,7 +29796,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="463" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>599</v>
       </c>
@@ -29801,7 +29849,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="464" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>600</v>
       </c>
@@ -29854,7 +29902,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="465" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>601</v>
       </c>
@@ -29907,7 +29955,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="466" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>602</v>
       </c>
@@ -29960,7 +30008,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="467" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>603</v>
       </c>
@@ -30013,7 +30061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>604</v>
       </c>
@@ -30066,7 +30114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>605</v>
       </c>
@@ -30119,7 +30167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>606</v>
       </c>
@@ -30172,7 +30220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>607</v>
       </c>
@@ -30225,7 +30273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>608</v>
       </c>
@@ -30278,7 +30326,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="473" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>609</v>
       </c>
@@ -30331,7 +30379,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="474" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>612</v>
       </c>
@@ -30384,7 +30432,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="475" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>613</v>
       </c>
@@ -30437,7 +30485,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="476" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>614</v>
       </c>
@@ -30490,7 +30538,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="477" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>615</v>
       </c>
@@ -30543,7 +30591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="478" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>616</v>
       </c>
@@ -30596,7 +30644,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="479" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>617</v>
       </c>
@@ -30649,7 +30697,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="480" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>618</v>
       </c>
@@ -30702,7 +30750,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="481" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>619</v>
       </c>
@@ -30755,7 +30803,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="482" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>620</v>
       </c>
@@ -30808,7 +30856,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="483" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>621</v>
       </c>
@@ -30861,7 +30909,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="484" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>622</v>
       </c>
@@ -30914,7 +30962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>623</v>
       </c>
@@ -30967,7 +31015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>624</v>
       </c>
@@ -31020,7 +31068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>625</v>
       </c>
@@ -31073,7 +31121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>626</v>
       </c>
@@ -31126,7 +31174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>627</v>
       </c>
@@ -31179,7 +31227,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="490" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>628</v>
       </c>
@@ -31232,7 +31280,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="491" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>632</v>
       </c>
@@ -31285,7 +31333,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="492" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>633</v>
       </c>
@@ -31338,7 +31386,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="493" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>634</v>
       </c>
@@ -31391,7 +31439,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="494" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>635</v>
       </c>
@@ -31444,7 +31492,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="495" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>636</v>
       </c>
@@ -31497,7 +31545,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="496" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>637</v>
       </c>
@@ -31550,7 +31598,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="497" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>638</v>
       </c>
@@ -31603,7 +31651,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="498" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>639</v>
       </c>
@@ -31656,7 +31704,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="499" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>640</v>
       </c>
@@ -31709,7 +31757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>641</v>
       </c>
@@ -31762,7 +31810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>642</v>
       </c>
@@ -31815,7 +31863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>644</v>
       </c>
@@ -31868,7 +31916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>645</v>
       </c>
@@ -31921,7 +31969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>647</v>
       </c>
@@ -31974,7 +32022,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="505" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>648</v>
       </c>
@@ -32027,7 +32075,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="506" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>652</v>
       </c>
@@ -32080,7 +32128,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="507" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>653</v>
       </c>
@@ -32133,7 +32181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>654</v>
       </c>
@@ -32186,7 +32234,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="509" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>655</v>
       </c>
@@ -32239,7 +32287,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="510" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>656</v>
       </c>
@@ -32292,7 +32340,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="511" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>657</v>
       </c>
@@ -32345,7 +32393,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="512" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>658</v>
       </c>
@@ -32398,7 +32446,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="513" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>659</v>
       </c>
@@ -32451,7 +32499,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="514" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>660</v>
       </c>
@@ -32504,7 +32552,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="515" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>661</v>
       </c>
@@ -32557,7 +32605,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="516" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>662</v>
       </c>
@@ -32610,7 +32658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>664</v>
       </c>
@@ -32663,7 +32711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>665</v>
       </c>
@@ -32716,7 +32764,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="519" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>667</v>
       </c>
@@ -32769,7 +32817,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="520" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>668</v>
       </c>
@@ -32822,7 +32870,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="521" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>671</v>
       </c>
@@ -32875,7 +32923,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="522" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>672</v>
       </c>
@@ -32928,7 +32976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>673</v>
       </c>
@@ -32981,7 +33029,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="524" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>674</v>
       </c>
@@ -33034,7 +33082,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="525" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>675</v>
       </c>
@@ -33087,7 +33135,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="526" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>676</v>
       </c>
@@ -33140,7 +33188,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="527" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>678</v>
       </c>
@@ -33193,7 +33241,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="528" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>679</v>
       </c>
@@ -33246,7 +33294,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="529" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>680</v>
       </c>
@@ -33299,7 +33347,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="530" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>682</v>
       </c>
@@ -33352,7 +33400,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="531" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>683</v>
       </c>
@@ -33405,7 +33453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>684</v>
       </c>
@@ -33458,7 +33506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>685</v>
       </c>
@@ -33511,7 +33559,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="534" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>686</v>
       </c>
@@ -33564,7 +33612,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="535" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>687</v>
       </c>
@@ -33608,7 +33656,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="536" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>690</v>
       </c>
@@ -33652,7 +33700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>691</v>
       </c>
@@ -33696,7 +33744,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="538" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>692</v>
       </c>
@@ -33740,7 +33788,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="539" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>693</v>
       </c>
@@ -33784,7 +33832,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="540" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>694</v>
       </c>
@@ -33828,7 +33876,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="541" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>695</v>
       </c>
@@ -33872,7 +33920,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="542" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>696</v>
       </c>
@@ -33916,7 +33964,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="543" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>697</v>
       </c>
@@ -33960,7 +34008,7 @@
         <v>-2.2999999999999998</v>
       </c>
     </row>
-    <row r="544" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>698</v>
       </c>
@@ -34004,7 +34052,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="545" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>699</v>
       </c>
@@ -34048,7 +34096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>700</v>
       </c>
@@ -34092,7 +34140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>701</v>
       </c>
@@ -34136,7 +34184,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="548" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>702</v>
       </c>
@@ -34189,7 +34237,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="549" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>706</v>
       </c>
@@ -34242,7 +34290,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="550" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>707</v>
       </c>
@@ -34295,7 +34343,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="551" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>708</v>
       </c>
@@ -34348,7 +34396,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="552" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>709</v>
       </c>
@@ -34401,7 +34449,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="553" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
         <v>710</v>
       </c>
@@ -34454,7 +34502,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="554" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>711</v>
       </c>
@@ -34507,7 +34555,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="555" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>712</v>
       </c>
@@ -34560,7 +34608,7 @@
         <v>-0.9</v>
       </c>
     </row>
-    <row r="556" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
         <v>713</v>
       </c>
@@ -34613,7 +34661,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="557" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
         <v>714</v>
       </c>
@@ -34666,7 +34714,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="558" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>715</v>
       </c>
@@ -34719,7 +34767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>716</v>
       </c>
@@ -34772,7 +34820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>717</v>
       </c>
@@ -34825,7 +34873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>718</v>
       </c>
@@ -34878,7 +34926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>719</v>
       </c>
@@ -34931,7 +34979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>720</v>
       </c>
@@ -34984,7 +35032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>721</v>
       </c>
@@ -35037,7 +35085,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="565" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>722</v>
       </c>
@@ -35090,7 +35138,7 @@
         <v>-4.7</v>
       </c>
     </row>
-    <row r="566" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>725</v>
       </c>
@@ -35143,7 +35191,7 @@
         <v>-4.7</v>
       </c>
     </row>
-    <row r="567" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>727</v>
       </c>
@@ -35196,7 +35244,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="568" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>728</v>
       </c>
@@ -35249,7 +35297,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="569" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>729</v>
       </c>
@@ -35302,7 +35350,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="570" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>730</v>
       </c>
@@ -35355,7 +35403,7 @@
         <v>-5.0999999999999996</v>
       </c>
     </row>
-    <row r="571" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>732</v>
       </c>
@@ -35408,7 +35456,7 @@
         <v>-5.0999999999999996</v>
       </c>
     </row>
-    <row r="572" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>734</v>
       </c>
@@ -35461,7 +35509,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="573" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>736</v>
       </c>
@@ -35514,7 +35562,7 @@
         <v>-3.6</v>
       </c>
     </row>
-    <row r="574" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>738</v>
       </c>
@@ -35567,7 +35615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>740</v>
       </c>
@@ -35620,7 +35668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>741</v>
       </c>
@@ -35673,7 +35721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>742</v>
       </c>
@@ -35726,7 +35774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>743</v>
       </c>
@@ -35779,7 +35827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>745</v>
       </c>
@@ -35832,7 +35880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>747</v>
       </c>
@@ -35885,7 +35933,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="581" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>750</v>
       </c>
@@ -35938,7 +35986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="582" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>751</v>
       </c>
@@ -35991,7 +36039,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="583" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>752</v>
       </c>
@@ -36044,7 +36092,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="584" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>753</v>
       </c>
@@ -36097,7 +36145,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="585" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>754</v>
       </c>
@@ -36150,7 +36198,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="586" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>755</v>
       </c>
@@ -36203,7 +36251,7 @@
         <v>-2.9</v>
       </c>
     </row>
-    <row r="587" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>756</v>
       </c>
@@ -36256,7 +36304,7 @@
         <v>-2.9</v>
       </c>
     </row>
-    <row r="588" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
         <v>757</v>
       </c>
@@ -36309,7 +36357,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="589" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
         <v>758</v>
       </c>
@@ -36362,7 +36410,7 @@
         <v>-3.8</v>
       </c>
     </row>
-    <row r="590" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
         <v>759</v>
       </c>
@@ -36415,7 +36463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
         <v>760</v>
       </c>
@@ -36468,7 +36516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>761</v>
       </c>
@@ -36521,7 +36569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
         <v>762</v>
       </c>
@@ -36574,7 +36622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
         <v>763</v>
       </c>
@@ -36627,7 +36675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
         <v>764</v>
       </c>
@@ -36680,7 +36728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
         <v>765</v>
       </c>
@@ -36733,7 +36781,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="597" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
         <v>766</v>
       </c>
@@ -36792,7 +36840,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="598" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
         <v>770</v>
       </c>
@@ -36851,7 +36899,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="599" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C599" t="s">
         <v>768</v>
       </c>
@@ -36871,7 +36919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C600" t="s">
         <v>768</v>
       </c>
@@ -36891,7 +36939,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="601" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C601" t="s">
         <v>768</v>
       </c>
@@ -36911,7 +36959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C602" t="s">
         <v>768</v>
       </c>
@@ -36931,7 +36979,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="603" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
         <v>771</v>
       </c>
@@ -36990,7 +37038,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="604" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
         <v>774</v>
       </c>
@@ -37049,7 +37097,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="605" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
         <v>775</v>
       </c>
@@ -37108,7 +37156,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="606" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
         <v>776</v>
       </c>
@@ -37167,7 +37215,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="607" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
         <v>777</v>
       </c>
@@ -37226,7 +37274,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="608" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
         <v>778</v>
       </c>
@@ -37285,7 +37333,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="609" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
         <v>779</v>
       </c>
@@ -37344,7 +37392,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="610" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
         <v>780</v>
       </c>
@@ -37403,7 +37451,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="611" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
         <v>781</v>
       </c>
@@ -37462,7 +37510,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="612" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
         <v>782</v>
       </c>
@@ -37521,7 +37569,7 @@
         <v>-1.8</v>
       </c>
     </row>
-    <row r="613" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
         <v>783</v>
       </c>
@@ -37580,7 +37628,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="614" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C614" t="s">
         <v>773</v>
       </c>
@@ -37600,7 +37648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C615" t="s">
         <v>773</v>
       </c>
@@ -37620,7 +37668,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="616" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C616" t="s">
         <v>773</v>
       </c>
@@ -37640,7 +37688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C617" t="s">
         <v>773</v>
       </c>
@@ -37660,7 +37708,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="618" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C618" t="s">
         <v>773</v>
       </c>
@@ -37680,7 +37728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
         <v>784</v>
       </c>
@@ -37739,7 +37787,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="620" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
         <v>785</v>
       </c>
@@ -37783,7 +37831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="621" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
         <v>789</v>
       </c>
@@ -37827,7 +37875,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="622" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
         <v>790</v>
       </c>
@@ -37871,7 +37919,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="623" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
         <v>791</v>
       </c>
@@ -37915,7 +37963,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="624" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
         <v>792</v>
       </c>
@@ -37959,7 +38007,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="625" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
         <v>793</v>
       </c>
@@ -38003,7 +38051,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="626" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
         <v>794</v>
       </c>
@@ -38047,7 +38095,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="627" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
         <v>795</v>
       </c>
@@ -38091,7 +38139,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="628" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
         <v>796</v>
       </c>
@@ -38135,7 +38183,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="629" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
         <v>797</v>
       </c>
@@ -38179,7 +38227,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="630" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
         <v>798</v>
       </c>
@@ -38223,7 +38271,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="631" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
         <v>799</v>
       </c>
@@ -38267,7 +38315,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="632" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
         <v>801</v>
       </c>
@@ -38311,7 +38359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="633" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
         <v>802</v>
       </c>
@@ -38355,7 +38403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
         <v>804</v>
       </c>
@@ -38399,7 +38447,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="635" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
         <v>805</v>
       </c>
@@ -38458,7 +38506,7 @@
         <v>-3.3</v>
       </c>
     </row>
-    <row r="636" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
         <v>809</v>
       </c>
@@ -38517,7 +38565,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="637" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C637" t="s">
         <v>807</v>
       </c>
@@ -38537,7 +38585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="638" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C638" t="s">
         <v>807</v>
       </c>
@@ -38557,7 +38605,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="639" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C639" t="s">
         <v>807</v>
       </c>
@@ -38577,7 +38625,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="640" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C640" t="s">
         <v>807</v>
       </c>
@@ -38597,7 +38645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="641" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C641" t="s">
         <v>807</v>
       </c>
@@ -38617,7 +38665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C642" t="s">
         <v>807</v>
       </c>
@@ -38637,7 +38685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C643" t="s">
         <v>807</v>
       </c>
@@ -38657,7 +38705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C644" t="s">
         <v>807</v>
       </c>
@@ -38677,7 +38725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C645" t="s">
         <v>807</v>
       </c>
@@ -38697,7 +38745,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="646" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
         <v>810</v>
       </c>
@@ -38756,7 +38804,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="647" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
         <v>814</v>
       </c>
@@ -38815,7 +38863,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="648" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
         <v>815</v>
       </c>
@@ -38874,7 +38922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="649" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
         <v>816</v>
       </c>
@@ -38933,7 +38981,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="650" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
         <v>817</v>
       </c>
@@ -38992,7 +39040,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="651" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
         <v>818</v>
       </c>
@@ -39051,7 +39099,7 @@
         <v>-3.2</v>
       </c>
     </row>
-    <row r="652" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A652" t="s">
         <v>819</v>
       </c>
@@ -39110,7 +39158,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="653" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
         <v>820</v>
       </c>
@@ -39169,7 +39217,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="654" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
         <v>821</v>
       </c>
@@ -39228,7 +39276,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="655" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C655" t="s">
         <v>812</v>
       </c>
@@ -39248,7 +39296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C656" t="s">
         <v>812</v>
       </c>
@@ -39268,7 +39316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C657" t="s">
         <v>812</v>
       </c>
@@ -39288,7 +39336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C658" t="s">
         <v>812</v>
       </c>
@@ -39308,7 +39356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C659" t="s">
         <v>812</v>
       </c>
@@ -39328,7 +39376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="660" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A660" t="s">
         <v>822</v>
       </c>
@@ -39387,7 +39435,7 @@
         <v>-0.9</v>
       </c>
     </row>
-    <row r="661" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C661" t="s">
         <v>824</v>
       </c>
@@ -39407,7 +39455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="662" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C662" t="s">
         <v>824</v>
       </c>
@@ -39427,7 +39475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C663" t="s">
         <v>824</v>
       </c>
@@ -39447,7 +39495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C664" t="s">
         <v>824</v>
       </c>
@@ -39467,7 +39515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C665" t="s">
         <v>824</v>
       </c>
@@ -39487,7 +39535,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="666" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A666" t="s">
         <v>827</v>
       </c>
@@ -39546,7 +39594,7 @@
         <v>-7.9</v>
       </c>
     </row>
-    <row r="667" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A667" t="s">
         <v>831</v>
       </c>
@@ -39605,7 +39653,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="668" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
         <v>832</v>
       </c>
@@ -39664,7 +39712,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="669" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
         <v>833</v>
       </c>
@@ -39723,7 +39771,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="670" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
         <v>834</v>
       </c>
@@ -39782,7 +39830,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="671" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
         <v>835</v>
       </c>
@@ -39841,7 +39889,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="672" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A672" t="s">
         <v>836</v>
       </c>
@@ -39900,7 +39948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A673" t="s">
         <v>837</v>
       </c>
@@ -39959,7 +40007,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="674" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A674" t="s">
         <v>838</v>
       </c>
@@ -40018,7 +40066,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="675" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A675" t="s">
         <v>839</v>
       </c>
@@ -40077,7 +40125,7 @@
         <v>-2.4</v>
       </c>
     </row>
-    <row r="676" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A676" t="s">
         <v>840</v>
       </c>
@@ -40136,7 +40184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="677" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A677" t="s">
         <v>841</v>
       </c>
@@ -40195,7 +40243,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="678" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A678" t="s">
         <v>842</v>
       </c>
@@ -40254,7 +40302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A679" t="s">
         <v>843</v>
       </c>
@@ -40313,7 +40361,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="680" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A680" t="s">
         <v>844</v>
       </c>
@@ -40372,7 +40420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A681" t="s">
         <v>845</v>
       </c>
@@ -40431,7 +40479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A682" t="s">
         <v>846</v>
       </c>
@@ -40490,7 +40538,7 @@
         <v>-19.8</v>
       </c>
     </row>
-    <row r="683" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A683" t="s">
         <v>847</v>
       </c>
@@ -40549,7 +40597,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="684" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A684" t="s">
         <v>850</v>
       </c>
@@ -40608,7 +40656,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="685" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A685" t="s">
         <v>851</v>
       </c>
@@ -40667,7 +40715,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="686" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A686" t="s">
         <v>852</v>
       </c>
@@ -40726,7 +40774,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="687" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A687" t="s">
         <v>853</v>
       </c>
@@ -40785,7 +40833,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="688" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A688" t="s">
         <v>854</v>
       </c>
@@ -40844,7 +40892,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="689" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A689" t="s">
         <v>855</v>
       </c>
@@ -40903,7 +40951,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="690" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A690" t="s">
         <v>856</v>
       </c>
@@ -40962,7 +41010,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="691" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A691" t="s">
         <v>857</v>
       </c>
@@ -41021,7 +41069,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="692" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A692" t="s">
         <v>858</v>
       </c>
@@ -41080,7 +41128,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="693" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A693" t="s">
         <v>859</v>
       </c>
@@ -41139,7 +41187,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="694" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A694" t="s">
         <v>860</v>
       </c>
@@ -41198,7 +41246,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="695" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A695" t="s">
         <v>861</v>
       </c>
@@ -41257,7 +41305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="696" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A696" t="s">
         <v>862</v>
       </c>
@@ -41316,7 +41364,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="697" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A697" t="s">
         <v>863</v>
       </c>
@@ -41375,7 +41423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="698" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A698" t="s">
         <v>864</v>
       </c>
@@ -41434,7 +41482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="699" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A699" t="s">
         <v>865</v>
       </c>
@@ -41493,7 +41541,7 @@
         <v>-11.3</v>
       </c>
     </row>
-    <row r="700" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C700" t="s">
         <v>868</v>
       </c>
@@ -41513,7 +41561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="701" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C701" t="s">
         <v>868</v>
       </c>
@@ -41533,7 +41581,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="702" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C702" t="s">
         <v>868</v>
       </c>
@@ -41553,7 +41601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C703" t="s">
         <v>868</v>
       </c>
@@ -41573,7 +41621,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="704" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
         <v>866</v>
       </c>
@@ -41632,7 +41680,7 @@
         <v>-0.9</v>
       </c>
     </row>
-    <row r="705" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C705" t="s">
         <v>872</v>
       </c>
@@ -41652,7 +41700,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="706" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C706" t="s">
         <v>872</v>
       </c>
@@ -41672,7 +41720,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="707" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C707" t="s">
         <v>872</v>
       </c>
@@ -41692,7 +41740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A708" t="s">
         <v>870</v>
       </c>
@@ -41751,7 +41799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A709" t="s">
         <v>875</v>
       </c>
@@ -41810,7 +41858,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="710" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A710" t="s">
         <v>876</v>
       </c>
@@ -41869,7 +41917,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="711" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A711" t="s">
         <v>880</v>
       </c>
@@ -41928,7 +41976,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="712" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C712" t="s">
         <v>878</v>
       </c>
@@ -41948,7 +41996,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="713" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C713" t="s">
         <v>878</v>
       </c>
@@ -41968,7 +42016,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="714" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C714" t="s">
         <v>878</v>
       </c>
@@ -41988,7 +42036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C715" t="s">
         <v>878</v>
       </c>
@@ -42008,7 +42056,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="716" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C716" t="s">
         <v>878</v>
       </c>
@@ -42028,7 +42076,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="717" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C717" t="s">
         <v>882</v>
       </c>
@@ -42048,7 +42096,7 @@
         <v>-2.7</v>
       </c>
     </row>
-    <row r="718" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C718" t="s">
         <v>882</v>
       </c>
@@ -42095,7 +42143,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="719" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C719" t="s">
         <v>882</v>
       </c>
@@ -42115,7 +42163,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="720" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C720" t="s">
         <v>882</v>
       </c>
@@ -42135,7 +42183,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="721" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C721" t="s">
         <v>882</v>
       </c>
@@ -42155,7 +42203,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="722" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C722" t="s">
         <v>882</v>
       </c>
@@ -42175,7 +42223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A723" t="s">
         <v>884</v>
       </c>
@@ -42234,7 +42282,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="724" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C724" t="s">
         <v>882</v>
       </c>
@@ -42269,7 +42317,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="725" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C725" t="s">
         <v>882</v>
       </c>
@@ -42289,7 +42337,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="726" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A726" t="s">
         <v>886</v>
       </c>
@@ -42348,7 +42396,7 @@
         <v>-27.3</v>
       </c>
     </row>
-    <row r="727" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A727" t="s">
         <v>890</v>
       </c>
@@ -42407,7 +42455,7 @@
         <v>-18.5</v>
       </c>
     </row>
-    <row r="728" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A728" t="s">
         <v>891</v>
       </c>
@@ -42466,7 +42514,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="729" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A729" t="s">
         <v>892</v>
       </c>
@@ -42525,7 +42573,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="730" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A730" t="s">
         <v>893</v>
       </c>
@@ -42584,7 +42632,7 @@
         <v>-10.5</v>
       </c>
     </row>
-    <row r="731" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A731" t="s">
         <v>894</v>
       </c>
@@ -42643,7 +42691,7 @@
         <v>-3.1</v>
       </c>
     </row>
-    <row r="732" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A732" t="s">
         <v>895</v>
       </c>
@@ -42702,7 +42750,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="733" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A733" t="s">
         <v>899</v>
       </c>
@@ -42761,7 +42809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="734" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A734" t="s">
         <v>902</v>
       </c>
@@ -42820,7 +42868,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="735" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A735" t="s">
         <v>903</v>
       </c>
@@ -42879,7 +42927,7 @@
         <v>-2.4</v>
       </c>
     </row>
-    <row r="736" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A736" t="s">
         <v>907</v>
       </c>
@@ -42938,7 +42986,7 @@
         <v>-3.4</v>
       </c>
     </row>
-    <row r="737" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A737" t="s">
         <v>908</v>
       </c>
@@ -42997,7 +43045,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="738" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A738" t="s">
         <v>909</v>
       </c>
@@ -43056,7 +43104,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="739" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A739" t="s">
         <v>910</v>
       </c>
@@ -43115,7 +43163,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="740" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A740" t="s">
         <v>911</v>
       </c>
@@ -43174,7 +43222,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="741" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A741" t="s">
         <v>912</v>
       </c>
@@ -43233,7 +43281,7 @@
         <v>-4.4000000000000004</v>
       </c>
     </row>
-    <row r="742" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A742" t="s">
         <v>913</v>
       </c>
@@ -43292,7 +43340,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="743" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A743" t="s">
         <v>914</v>
       </c>
@@ -43351,7 +43399,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="744" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A744" t="s">
         <v>915</v>
       </c>
@@ -43410,7 +43458,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="745" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A745" t="s">
         <v>916</v>
       </c>
@@ -43469,7 +43517,7 @@
         <v>-2.4</v>
       </c>
     </row>
-    <row r="746" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A746" t="s">
         <v>917</v>
       </c>
@@ -43528,7 +43576,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="747" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A747" t="s">
         <v>918</v>
       </c>
@@ -43587,7 +43635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="748" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A748" t="s">
         <v>919</v>
       </c>
@@ -43646,7 +43694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="749" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A749" t="s">
         <v>920</v>
       </c>
@@ -43705,7 +43753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="750" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A750" t="s">
         <v>921</v>
       </c>
@@ -43764,7 +43812,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="751" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A751" t="s">
         <v>923</v>
       </c>
@@ -43823,7 +43871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="752" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A752" t="s">
         <v>924</v>
       </c>
@@ -43882,7 +43930,7 @@
         <v>-0.9</v>
       </c>
     </row>
-    <row r="753" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A753" t="s">
         <v>928</v>
       </c>
@@ -43941,7 +43989,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="754" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A754" t="s">
         <v>929</v>
       </c>
@@ -44000,7 +44048,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="755" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A755" t="s">
         <v>930</v>
       </c>
@@ -44059,7 +44107,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="756" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A756" t="s">
         <v>931</v>
       </c>
@@ -44118,7 +44166,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="757" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A757" t="s">
         <v>932</v>
       </c>
@@ -44177,7 +44225,7 @@
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="758" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A758" t="s">
         <v>933</v>
       </c>
@@ -44236,7 +44284,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="759" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A759" t="s">
         <v>934</v>
       </c>
@@ -44295,7 +44343,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="760" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A760" t="s">
         <v>935</v>
       </c>
@@ -44354,7 +44402,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="761" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A761" t="s">
         <v>936</v>
       </c>
@@ -44413,7 +44461,7 @@
         <v>-72.5</v>
       </c>
     </row>
-    <row r="762" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A762" t="s">
         <v>940</v>
       </c>
@@ -44472,7 +44520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="763" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A763" t="s">
         <v>947</v>
       </c>
@@ -44519,7 +44567,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="764" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C764" t="s">
         <v>949</v>
       </c>
@@ -44539,7 +44587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="765" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C765" t="s">
         <v>949</v>
       </c>
@@ -44559,7 +44607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="766" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C766" t="s">
         <v>949</v>
       </c>
@@ -44579,7 +44627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="767" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C767" t="s">
         <v>949</v>
       </c>
@@ -44599,7 +44647,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="768" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C768" t="s">
         <v>949</v>
       </c>
@@ -44619,7 +44667,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="769" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A769" t="s">
         <v>952</v>
       </c>
@@ -44672,7 +44720,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="770" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A770" t="s">
         <v>956</v>
       </c>
@@ -44725,7 +44773,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="771" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A771" t="s">
         <v>957</v>
       </c>
@@ -44778,7 +44826,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="772" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A772" t="s">
         <v>958</v>
       </c>
@@ -44831,7 +44879,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="773" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A773" t="s">
         <v>959</v>
       </c>
@@ -44884,7 +44932,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="774" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A774" t="s">
         <v>960</v>
       </c>
@@ -44937,7 +44985,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="775" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A775" t="s">
         <v>961</v>
       </c>
@@ -44990,7 +45038,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="776" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A776" t="s">
         <v>962</v>
       </c>
@@ -45043,7 +45091,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="777" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A777" t="s">
         <v>963</v>
       </c>
@@ -45096,7 +45144,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="778" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A778" t="s">
         <v>964</v>
       </c>
@@ -45149,7 +45197,7 @@
         <v>-3.3</v>
       </c>
     </row>
-    <row r="779" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A779" t="s">
         <v>965</v>
       </c>
@@ -45202,7 +45250,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="780" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A780" t="s">
         <v>966</v>
       </c>
@@ -45255,7 +45303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="781" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A781" t="s">
         <v>967</v>
       </c>
@@ -45308,7 +45356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="782" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A782" t="s">
         <v>968</v>
       </c>
@@ -45361,7 +45409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="783" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A783" t="s">
         <v>969</v>
       </c>
@@ -45414,7 +45462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="784" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A784" t="s">
         <v>970</v>
       </c>
@@ -45467,7 +45515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="785" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A785" t="s">
         <v>971</v>
       </c>
@@ -45520,7 +45568,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="786" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A786" t="s">
         <v>972</v>
       </c>
@@ -45573,7 +45621,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="787" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A787" t="s">
         <v>975</v>
       </c>
@@ -45626,7 +45674,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="788" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A788" t="s">
         <v>976</v>
       </c>
@@ -45679,7 +45727,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="789" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A789" t="s">
         <v>977</v>
       </c>
@@ -45732,7 +45780,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="790" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A790" t="s">
         <v>978</v>
       </c>
@@ -45785,7 +45833,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="791" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A791" t="s">
         <v>979</v>
       </c>
@@ -45838,7 +45886,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="792" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A792" t="s">
         <v>980</v>
       </c>
@@ -45891,7 +45939,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="793" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A793" t="s">
         <v>981</v>
       </c>
@@ -45944,7 +45992,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="794" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A794" t="s">
         <v>982</v>
       </c>
@@ -45997,7 +46045,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="795" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A795" t="s">
         <v>983</v>
       </c>
@@ -46050,7 +46098,7 @@
         <v>-3.6</v>
       </c>
     </row>
-    <row r="796" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A796" t="s">
         <v>984</v>
       </c>
@@ -46103,7 +46151,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="797" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A797" t="s">
         <v>985</v>
       </c>
@@ -46156,7 +46204,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="798" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A798" t="s">
         <v>986</v>
       </c>
@@ -46209,7 +46257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="799" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A799" t="s">
         <v>987</v>
       </c>
@@ -46262,7 +46310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="800" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A800" t="s">
         <v>988</v>
       </c>
@@ -46315,7 +46363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="801" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A801" t="s">
         <v>989</v>
       </c>
@@ -46368,7 +46416,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="802" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A802" t="s">
         <v>990</v>
       </c>
@@ -46421,7 +46469,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="803" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A803" t="s">
         <v>991</v>
       </c>
@@ -46474,7 +46522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="804" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A804" t="s">
         <v>995</v>
       </c>
@@ -46527,7 +46575,7 @@
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="805" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A805" t="s">
         <v>996</v>
       </c>
@@ -46568,7 +46616,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="806" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A806" t="s">
         <v>998</v>
       </c>
@@ -46621,7 +46669,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="807" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A807" t="s">
         <v>999</v>
       </c>
@@ -46674,7 +46722,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="808" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A808" t="s">
         <v>1000</v>
       </c>
@@ -46727,7 +46775,7 @@
         <v>-4.7</v>
       </c>
     </row>
-    <row r="809" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A809" t="s">
         <v>1002</v>
       </c>
@@ -46780,7 +46828,7 @@
         <v>-4.7</v>
       </c>
     </row>
-    <row r="810" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A810" t="s">
         <v>1004</v>
       </c>
@@ -46833,7 +46881,7 @@
         <v>-0.9</v>
       </c>
     </row>
-    <row r="811" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A811" t="s">
         <v>1005</v>
       </c>
@@ -46886,7 +46934,7 @@
         <v>-3.7</v>
       </c>
     </row>
-    <row r="812" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A812" t="s">
         <v>1006</v>
       </c>
@@ -46939,7 +46987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="813" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A813" t="s">
         <v>1008</v>
       </c>
@@ -46992,7 +47040,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="814" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A814" t="s">
         <v>1009</v>
       </c>
@@ -47045,7 +47093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="815" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A815" t="s">
         <v>1011</v>
       </c>
@@ -47098,7 +47146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="816" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A816" t="s">
         <v>1012</v>
       </c>
@@ -47151,7 +47199,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="817" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A817" t="s">
         <v>1014</v>
       </c>
@@ -47204,7 +47252,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="818" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A818" t="s">
         <v>1015</v>
       </c>
@@ -47248,7 +47296,7 @@
         <v>-2.9</v>
       </c>
     </row>
-    <row r="819" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A819" t="s">
         <v>1019</v>
       </c>
@@ -47292,7 +47340,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="820" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A820" t="s">
         <v>1020</v>
       </c>
@@ -47336,7 +47384,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="821" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A821" t="s">
         <v>1021</v>
       </c>
@@ -47380,7 +47428,7 @@
         <v>46.1</v>
       </c>
     </row>
-    <row r="822" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A822" t="s">
         <v>1022</v>
       </c>
@@ -47424,7 +47472,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="823" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A823" t="s">
         <v>1023</v>
       </c>
@@ -47468,7 +47516,7 @@
         <v>46.3</v>
       </c>
     </row>
-    <row r="824" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A824" t="s">
         <v>1024</v>
       </c>
@@ -47512,7 +47560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="825" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A825" t="s">
         <v>1025</v>
       </c>
@@ -47556,7 +47604,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="826" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A826" t="s">
         <v>1026</v>
       </c>
@@ -47600,7 +47648,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="827" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A827" t="s">
         <v>1027</v>
       </c>
@@ -47644,7 +47692,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="828" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A828" t="s">
         <v>1028</v>
       </c>
@@ -47688,7 +47736,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="829" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A829" t="s">
         <v>1029</v>
       </c>
@@ -47732,7 +47780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="830" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A830" t="s">
         <v>1030</v>
       </c>
@@ -47776,7 +47824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="831" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A831" t="s">
         <v>1031</v>
       </c>
@@ -47820,7 +47868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="832" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A832" t="s">
         <v>1032</v>
       </c>
@@ -47864,7 +47912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="833" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A833" t="s">
         <v>1033</v>
       </c>
@@ -47908,7 +47956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="834" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A834" t="s">
         <v>1034</v>
       </c>
@@ -47952,7 +48000,7 @@
         <v>-3.1</v>
       </c>
     </row>
-    <row r="835" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A835" t="s">
         <v>1035</v>
       </c>
@@ -48005,7 +48053,7 @@
         <v>-2.2000000000000002</v>
       </c>
     </row>
-    <row r="836" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A836" t="s">
         <v>1038</v>
       </c>
@@ -48058,7 +48106,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="837" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A837" t="s">
         <v>1039</v>
       </c>
@@ -48111,7 +48159,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="838" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A838" t="s">
         <v>1040</v>
       </c>
@@ -48164,7 +48212,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="839" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A839" t="s">
         <v>1041</v>
       </c>
@@ -48217,7 +48265,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="840" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A840" t="s">
         <v>1042</v>
       </c>
@@ -48270,7 +48318,7 @@
         <v>44.4</v>
       </c>
     </row>
-    <row r="841" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A841" t="s">
         <v>1043</v>
       </c>
@@ -48323,7 +48371,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="842" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A842" t="s">
         <v>1044</v>
       </c>
@@ -48376,7 +48424,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="843" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A843" t="s">
         <v>1045</v>
       </c>
@@ -48429,7 +48477,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="844" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A844" t="s">
         <v>1046</v>
       </c>
@@ -48482,7 +48530,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="845" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A845" t="s">
         <v>1047</v>
       </c>
@@ -48535,7 +48583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="846" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A846" t="s">
         <v>1048</v>
       </c>
@@ -48588,7 +48636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="847" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A847" t="s">
         <v>1049</v>
       </c>
@@ -48641,7 +48689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="848" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A848" t="s">
         <v>1050</v>
       </c>
@@ -48694,7 +48742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="849" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A849" t="s">
         <v>1051</v>
       </c>
@@ -48747,7 +48795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="850" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A850" t="s">
         <v>1052</v>
       </c>
@@ -48800,7 +48848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="851" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A851" t="s">
         <v>1053</v>
       </c>
@@ -48853,7 +48901,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="852" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A852" t="s">
         <v>1055</v>
       </c>
@@ -48906,7 +48954,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="853" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
         <v>1059</v>
       </c>
@@ -48959,7 +49007,7 @@
         <v>-2.6</v>
       </c>
     </row>
-    <row r="854" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A854" t="s">
         <v>1060</v>
       </c>
@@ -49012,7 +49060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="855" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
         <v>1061</v>
       </c>
@@ -49065,7 +49113,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="856" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A856" t="s">
         <v>1062</v>
       </c>
@@ -49118,7 +49166,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="857" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A857" t="s">
         <v>1063</v>
       </c>
@@ -49171,7 +49219,7 @@
         <v>-2.2000000000000002</v>
       </c>
     </row>
-    <row r="858" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A858" t="s">
         <v>1064</v>
       </c>
@@ -49224,7 +49272,7 @@
         <v>-3.1</v>
       </c>
     </row>
-    <row r="859" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A859" t="s">
         <v>1065</v>
       </c>
@@ -49277,7 +49325,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="860" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A860" t="s">
         <v>1066</v>
       </c>
@@ -49330,7 +49378,7 @@
         <v>-2.6</v>
       </c>
     </row>
-    <row r="861" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A861" t="s">
         <v>1067</v>
       </c>
@@ -49383,7 +49431,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="862" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A862" t="s">
         <v>1068</v>
       </c>
@@ -49436,7 +49484,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="863" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A863" t="s">
         <v>1069</v>
       </c>
@@ -49489,7 +49537,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="864" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A864" t="s">
         <v>1071</v>
       </c>
@@ -49542,7 +49590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="865" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A865" t="s">
         <v>1072</v>
       </c>
@@ -49595,7 +49643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="866" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A866" t="s">
         <v>1074</v>
       </c>
@@ -49648,7 +49696,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="867" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A867" t="s">
         <v>1075</v>
       </c>
@@ -49701,7 +49749,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="868" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A868" t="s">
         <v>1079</v>
       </c>
@@ -49754,7 +49802,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="869" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A869" t="s">
         <v>1080</v>
       </c>
@@ -49807,7 +49855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="870" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A870" t="s">
         <v>1081</v>
       </c>
@@ -49860,7 +49908,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="871" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A871" t="s">
         <v>1082</v>
       </c>
@@ -49913,7 +49961,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="872" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A872" t="s">
         <v>1083</v>
       </c>
@@ -49966,7 +50014,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="873" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A873" t="s">
         <v>1084</v>
       </c>
@@ -50019,7 +50067,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="874" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A874" t="s">
         <v>1085</v>
       </c>
@@ -50072,7 +50120,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="875" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A875" t="s">
         <v>1086</v>
       </c>
@@ -50125,7 +50173,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="876" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A876" t="s">
         <v>1087</v>
       </c>
@@ -50178,7 +50226,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="877" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A877" t="s">
         <v>1088</v>
       </c>
@@ -50231,7 +50279,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="878" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A878" t="s">
         <v>1089</v>
       </c>
@@ -50284,7 +50332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="879" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A879" t="s">
         <v>1090</v>
       </c>
@@ -50337,7 +50385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="880" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A880" t="s">
         <v>1091</v>
       </c>
@@ -50390,7 +50438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="881" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A881" t="s">
         <v>1092</v>
       </c>
@@ -50443,7 +50491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="882" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A882" t="s">
         <v>1093</v>
       </c>
@@ -50496,7 +50544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="883" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A883" t="s">
         <v>1094</v>
       </c>
@@ -50549,7 +50597,7 @@
         <v>-1.8</v>
       </c>
     </row>
-    <row r="884" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A884" t="s">
         <v>1095</v>
       </c>
@@ -50602,7 +50650,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="885" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A885" t="s">
         <v>1099</v>
       </c>
@@ -50655,7 +50703,7 @@
         <v>-3.9</v>
       </c>
     </row>
-    <row r="886" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A886" t="s">
         <v>1100</v>
       </c>
@@ -50708,7 +50756,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="887" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A887" t="s">
         <v>1101</v>
       </c>
@@ -50761,7 +50809,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="888" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A888" t="s">
         <v>1102</v>
       </c>
@@ -50814,7 +50862,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="889" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A889" t="s">
         <v>1103</v>
       </c>
@@ -50867,7 +50915,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="890" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A890" t="s">
         <v>1104</v>
       </c>
@@ -50920,7 +50968,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="891" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A891" t="s">
         <v>1105</v>
       </c>
@@ -50973,7 +51021,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="892" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A892" t="s">
         <v>1106</v>
       </c>
@@ -51026,7 +51074,7 @@
         <v>-0.9</v>
       </c>
     </row>
-    <row r="893" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A893" t="s">
         <v>1107</v>
       </c>
@@ -51079,7 +51127,7 @@
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="894" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A894" t="s">
         <v>1108</v>
       </c>
@@ -51132,7 +51180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="895" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A895" t="s">
         <v>1109</v>
       </c>
@@ -51185,7 +51233,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="896" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A896" t="s">
         <v>1110</v>
       </c>
@@ -51238,7 +51286,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="897" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A897" t="s">
         <v>1114</v>
       </c>
@@ -51291,7 +51339,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="898" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A898" t="s">
         <v>1115</v>
       </c>
@@ -51344,7 +51392,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="899" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A899" t="s">
         <v>1116</v>
       </c>
@@ -51397,7 +51445,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="900" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A900" t="s">
         <v>1117</v>
       </c>
@@ -51450,7 +51498,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="901" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A901" t="s">
         <v>1118</v>
       </c>
@@ -51503,7 +51551,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="902" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A902" t="s">
         <v>1119</v>
       </c>
@@ -51556,7 +51604,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="903" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A903" t="s">
         <v>1120</v>
       </c>
@@ -51609,7 +51657,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="904" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A904" t="s">
         <v>1121</v>
       </c>
@@ -51662,7 +51710,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="905" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A905" t="s">
         <v>1122</v>
       </c>
@@ -51715,7 +51763,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="906" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A906" t="s">
         <v>1123</v>
       </c>
@@ -51768,7 +51816,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="907" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A907" t="s">
         <v>1124</v>
       </c>
@@ -51821,7 +51869,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="908" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A908" t="s">
         <v>1125</v>
       </c>
@@ -51874,7 +51922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="909" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A909" t="s">
         <v>1126</v>
       </c>
@@ -51921,7 +51969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="910" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A910" t="s">
         <v>1127</v>
       </c>
@@ -51974,7 +52022,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="911" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A911" t="s">
         <v>1128</v>
       </c>
@@ -52021,7 +52069,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="912" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A912" t="s">
         <v>1132</v>
       </c>
@@ -52068,7 +52116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="913" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A913" t="s">
         <v>1133</v>
       </c>
@@ -52115,7 +52163,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="914" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A914" t="s">
         <v>1134</v>
       </c>
@@ -52162,7 +52210,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="915" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A915" t="s">
         <v>1135</v>
       </c>
@@ -52209,7 +52257,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="916" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A916" t="s">
         <v>1136</v>
       </c>
@@ -52256,7 +52304,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="917" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A917" t="s">
         <v>1137</v>
       </c>
@@ -52303,7 +52351,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="918" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A918" t="s">
         <v>1138</v>
       </c>
@@ -52350,7 +52398,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="919" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A919" t="s">
         <v>1139</v>
       </c>
@@ -52397,7 +52445,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="920" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A920" t="s">
         <v>1140</v>
       </c>
@@ -52444,7 +52492,7 @@
         <v>-3.6</v>
       </c>
     </row>
-    <row r="921" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A921" t="s">
         <v>1141</v>
       </c>
@@ -52491,7 +52539,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="922" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A922" t="s">
         <v>1142</v>
       </c>
@@ -52538,7 +52586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="923" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A923" t="s">
         <v>1143</v>
       </c>
@@ -52585,7 +52633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="924" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A924" t="s">
         <v>1144</v>
       </c>
@@ -52632,7 +52680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="925" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A925" t="s">
         <v>1145</v>
       </c>
@@ -52679,7 +52727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="926" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A926" t="s">
         <v>1146</v>
       </c>
@@ -52726,7 +52774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="927" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A927" t="s">
         <v>1147</v>
       </c>
@@ -52773,7 +52821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="928" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A928" t="s">
         <v>1148</v>
       </c>
@@ -52832,7 +52880,7 @@
         <v>-10.1</v>
       </c>
     </row>
-    <row r="929" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A929" t="s">
         <v>1152</v>
       </c>
@@ -52891,7 +52939,7 @@
         <v>-9.6999999999999993</v>
       </c>
     </row>
-    <row r="930" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A930" t="s">
         <v>1153</v>
       </c>
@@ -52950,7 +52998,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="931" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A931" t="s">
         <v>1154</v>
       </c>
@@ -53009,7 +53057,7 @@
         <v>39.4</v>
       </c>
     </row>
-    <row r="932" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A932" t="s">
         <v>1155</v>
       </c>
@@ -53068,7 +53116,7 @@
         <v>38.4</v>
       </c>
     </row>
-    <row r="933" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A933" t="s">
         <v>1156</v>
       </c>
@@ -53127,7 +53175,7 @@
         <v>-8.6999999999999993</v>
       </c>
     </row>
-    <row r="934" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A934" t="s">
         <v>1157</v>
       </c>
@@ -53186,7 +53234,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="935" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A935" t="s">
         <v>1158</v>
       </c>
@@ -53245,7 +53293,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="936" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A936" t="s">
         <v>1159</v>
       </c>
@@ -53304,7 +53352,7 @@
         <v>-1.8</v>
       </c>
     </row>
-    <row r="937" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A937" t="s">
         <v>1160</v>
       </c>
@@ -53363,7 +53411,7 @@
         <v>-5.8</v>
       </c>
     </row>
-    <row r="938" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A938" t="s">
         <v>1161</v>
       </c>
@@ -53422,7 +53470,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="939" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A939" t="s">
         <v>1162</v>
       </c>
@@ -53481,7 +53529,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="940" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A940" t="s">
         <v>1164</v>
       </c>
@@ -53540,7 +53588,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="941" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A941" t="s">
         <v>1165</v>
       </c>
@@ -53599,7 +53647,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="942" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A942" t="s">
         <v>1169</v>
       </c>
@@ -53658,7 +53706,7 @@
         <v>-6.7</v>
       </c>
     </row>
-    <row r="943" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A943" t="s">
         <v>1170</v>
       </c>
@@ -53717,7 +53765,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="944" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A944" t="s">
         <v>1171</v>
       </c>
@@ -53776,7 +53824,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="945" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A945" t="s">
         <v>1172</v>
       </c>
@@ -53835,7 +53883,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="946" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A946" t="s">
         <v>1173</v>
       </c>
@@ -53894,7 +53942,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="947" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A947" t="s">
         <v>1174</v>
       </c>
@@ -53953,7 +54001,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="948" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A948" t="s">
         <v>1175</v>
       </c>
@@ -54012,7 +54060,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="949" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A949" t="s">
         <v>1176</v>
       </c>
@@ -54071,7 +54119,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="950" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A950" t="s">
         <v>1177</v>
       </c>
@@ -54130,7 +54178,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="951" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A951" t="s">
         <v>1178</v>
       </c>
@@ -54189,7 +54237,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="952" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A952" t="s">
         <v>1179</v>
       </c>
@@ -54248,7 +54296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="953" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A953" t="s">
         <v>1180</v>
       </c>
@@ -54307,7 +54355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="954" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A954" t="s">
         <v>1181</v>
       </c>
@@ -54366,7 +54414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="955" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A955" t="s">
         <v>1182</v>
       </c>
@@ -54425,7 +54473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="956" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A956" t="s">
         <v>1183</v>
       </c>
@@ -54484,7 +54532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="957" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A957" t="s">
         <v>1184</v>
       </c>
